--- a/outputs/content-system-prompts/content-system-prompts-v0.1.xlsx
+++ b/outputs/content-system-prompts/content-system-prompts-v0.1.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt导入模板" sheetId="1" r:id="Rcffd66f7e6fd44dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="调用梳理" sheetId="2" r:id="R1df223cf9fe44a88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="确认重点" sheetId="3" r:id="Ra76f88060dbe48d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt导入模板" sheetId="1" r:id="R5dce10fb007c43cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="调用梳理" sheetId="2" r:id="Rb3431438706048bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="确认重点" sheetId="3" r:id="Rbc527cfc5a534882"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -320,7 +320,7 @@
 2. 每个切口必须包含：选题公式、推荐结构、时效判断、四维评分、标题方向、素材缺口。
 3. 四维评分包括：热爱程度、专业能力、市场需求、资源积累，每项 1-5 分。
 4. 优先推荐总分最高、最容易转成公众号观点文的切口。
-5. 输出必须能交给 content-brief-builder 继续生成 brief。</x:v>
+5. 输出必须能交给 content_outline_builder 继续生成文章大纲。</x:v>
       </x:c>
       <x:c r="E2" s="13" t="str">
         <x:v>选题,热点,上游决策</x:v>
@@ -334,31 +334,33 @@
     </x:row>
     <x:row r="3" ht="157.5" customHeight="1">
       <x:c r="A3" s="13" t="str">
-        <x:v>Brief</x:v>
+        <x:v>大纲</x:v>
       </x:c>
       <x:c r="B3" s="13" t="str">
-        <x:v>Content Brief Builder：结构化创作简报</x:v>
+        <x:v>Content Outline Builder：文章大纲</x:v>
       </x:c>
       <x:c r="C3" s="13" t="str">
-        <x:v>把已选题目整理成 stage-1 兼容 brief，锁定读者、核心观点、SCQA、素材和风险。</x:v>
+        <x:v>把已选题目整理成可确认、可写作的文章大纲，锁定读者、核心判断、SCQA、素材和风险。</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
-        <x:v>请把以下选题整理成结构化创作 brief，不写正文。
+        <x:v>请把以下选题整理成文章大纲 outline，不写正文。
 选题来源：{{选题来源}}
 主要想说：{{核心判断}}
 目标读者：{{目标读者}}
 希望读者看完做什么：{{发布目标}}
 已有素材：{{已有素材}}
 要求：
-1. 补全背景与语境、论证方向、可用案例 / 素材。
+1. 先锁定目标读者、读者痛点、核心判断、写作目的和切入角度。
 2. 角度必须是一句话、有立场、与众不同。
 3. 必须包含 SCQA：情境(S)、冲突(C)、问题(Q)、答案(A)。
-4. 素材至少 3 条，不足时标注推断或待验证。
-5. 必须包含明确不要写什么、风格要求、配图方向、风险提醒、素材来源可信度。
-6. 输出 section header 必须兼容 stage1 brief 模板。</x:v>
+4. 素材至少 3 条，每条标注来源可信度；不足时标注推断或待验证。
+5. 必须输出独立的文章大纲，不能用推荐框架代替大纲。
+6. 大纲每节必须包含：章节标题、要回答的问题、关键内容、可使用素材。
+7. 软件介绍或教程类选题必须覆盖实际使用路径：安装/入口、初始化、核心操作、典型工作流、权限/边界、维护方法。
+8. 必须包含风险提醒，并最后展示核心判断、切入角度、文章大纲摘要，等待确认。</x:v>
       </x:c>
       <x:c r="E3" s="13" t="str">
-        <x:v>brief,创作简报,SCQA</x:v>
+        <x:v>outline,文章大纲,SCQA</x:v>
       </x:c>
       <x:c r="F3" s="13" t="str">
         <x:v>copy</x:v>
@@ -372,13 +374,13 @@
         <x:v>采集</x:v>
       </x:c>
       <x:c r="B4" s="13" t="str">
-        <x:v>WeChat Collect：公众号原文转 Brief</x:v>
+        <x:v>WeChat Collect：公众号原文转 Outline</x:v>
       </x:c>
       <x:c r="C4" s="13" t="str">
-        <x:v>从公开公众号文章提取标题、正文、作者和链接，生成再创作 brief。</x:v>
+        <x:v>从公开公众号文章提取标题、正文、作者和链接，生成再创作 outline。</x:v>
       </x:c>
       <x:c r="D4" s="13" t="str">
-        <x:v>请基于以下公众号原文采集结果，生成可进入 stage-1 写作链路的再创作 brief。
+        <x:v>请基于以下公众号原文采集结果，生成可进入写作链路的再创作 outline。
 原文标题：{{原文标题}}
 原文作者 / 公众号：{{原文作者}}
 发布时间：{{发布时间}}
@@ -390,10 +392,10 @@
 2. 提炼核心观点、背景语境和 3 个论证方向。
 3. 可用素材必须包含来源链接和作者信息。
 4. 明确提醒不要复刻原文结构、句子、标题党和营销腔。
-5. 输出为 stage-1 兼容 brief。</x:v>
+5. 输出为 content-outline 兼容结构。</x:v>
       </x:c>
       <x:c r="E4" s="13" t="str">
-        <x:v>公众号采集,brief,再创作</x:v>
+        <x:v>公众号采集,outline,再创作</x:v>
       </x:c>
       <x:c r="F4" s="13" t="str">
         <x:v>copy</x:v>
@@ -423,7 +425,7 @@
 1. 汇总候选信息，保留标题、链接、来源、时间、热度和摘要。
 2. 推荐最多 3 个值得继续写的题目。
 3. 每个推荐题目补：推荐理由、写作角度、值得写评分、目标读者、核心痛点、标题方向、证据缺口和风险提醒。
-4. 输出适合作为 topic-research 或 content-brief-builder 的上游材料。</x:v>
+4. 输出适合作为 topic-research 或 content_outline_builder 的上游材料。</x:v>
       </x:c>
       <x:c r="E5" s="13" t="str">
         <x:v>资讯扫描,研究,选题</x:v>
@@ -474,15 +476,16 @@
         <x:v>Case Writer Hybrid：自动长文初稿</x:v>
       </x:c>
       <x:c r="C7" s="13" t="str">
-        <x:v>把结构化 brief 扩写为公众号长文，并生成 writing pack 与质量门控材料。</x:v>
+        <x:v>把结构化 outline 扩写为公众号长文，并生成 writing pack 与质量门控材料。</x:v>
       </x:c>
       <x:c r="D7" s="13" t="str">
-        <x:v>请基于以下结构化 brief 生成一篇公众号长文初稿。
+        <x:v>请基于以下结构化 outline 生成一篇公众号长文初稿。
 主题：{{topic}}
 目标读者：{{target_reader}}
 发布目标：{{publish_goal}}
 核心观点：{{core_view}}
 背景与语境：{{background}}
+文章大纲：{{outline}}
 论证方向：{{arguments}}
 可用案例 / 素材：{{cases}}
 明确不要写什么：{{avoid}}
@@ -491,8 +494,8 @@
 风险提醒：{{risk_reminders}}
 素材可信度：{{material_confidence}}
 要求：
-1. 保留用户提供的判断、框架和证据，优先使用 brief 里的论证方向。
-2. 结构包含标题、导语、问题提出、核心判断、论证段、结论、可传播总结。
+1. 保留用户提供的判断、文章大纲和证据，优先使用 outline 里的章节顺序。
+2. 结构包含标题、导语、问题提出、核心判断、章节展开、结论、可传播总结。
 3. 如素材可信度低，只能作为待验证线索，不可写成确定事实。
 4. 每段尽量短，先说观点再说理由。
 5. 输出可进入 writer -&gt; critic -&gt; humanizer-zh -&gt; judge 的本地质量循环。</x:v>
@@ -518,7 +521,7 @@
         <x:v>交互模式下先产出标题候选、结构选择和章节大纲，等待用户确认。</x:v>
       </x:c>
       <x:c r="D8" s="13" t="str">
-        <x:v>请先不要写全文，只基于 brief 输出标题和大纲供确认。
+        <x:v>请先不要写全文，只基于 outline 输出标题和大纲供确认。
 主题：{{topic}}
 目标读者：{{target_reader}}
 发布目标：{{publish_goal}}
@@ -646,7 +649,7 @@
         <x:v>Script Writer Short：文章转口播脚本</x:v>
       </x:c>
       <x:c r="C12" s="13" t="str">
-        <x:v>把文章、brief 或题目笔记转成 60-180 秒短视频口播脚本。</x:v>
+        <x:v>把文章、outline 或题目笔记转成 60-180 秒短视频口播脚本。</x:v>
       </x:c>
       <x:c r="D12" s="13" t="str">
         <x:v>请把以下文章或题目笔记转成短视频口播脚本。
@@ -806,13 +809,13 @@
     </x:row>
     <x:row r="3" ht="67.5" customHeight="1">
       <x:c r="A3" s="13" t="str">
-        <x:v>Brief</x:v>
+        <x:v>大纲</x:v>
       </x:c>
       <x:c r="B3" s="13" t="str">
-        <x:v>Content Brief Builder：结构化创作简报</x:v>
+        <x:v>Content Outline Builder：文章大纲</x:v>
       </x:c>
       <x:c r="C3" s="13" t="str">
-        <x:v>skills/content-brief-builder/SKILL.md; runtime.py</x:v>
+        <x:v>skills/content_outline_builder/SKILL.md</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
         <x:v>本地规则 + Skill 指令</x:v>
@@ -829,19 +832,19 @@
         <x:v>采集</x:v>
       </x:c>
       <x:c r="B4" s="13" t="str">
-        <x:v>WeChat Collect：公众号原文转 Brief</x:v>
+        <x:v>WeChat Collect：公众号原文转 Outline</x:v>
       </x:c>
       <x:c r="C4" s="13" t="str">
         <x:v>skills/wechat-collect/runtime.py</x:v>
       </x:c>
       <x:c r="D4" s="13" t="str">
-        <x:v>本地抽取 + brief 模板</x:v>
+        <x:v>本地抽取 + outline 模板</x:v>
       </x:c>
       <x:c r="E4" s="13" t="str">
         <x:v>{{原文标题}}, {{原文作者}}, {{发布时间}}, {{原文链接}}, {{正文摘要段落}}, {{小标题}}</x:v>
       </x:c>
       <x:c r="F4" s="13" t="str">
-        <x:v>是否和普通 Brief 合并，还是保留采集专用版本</x:v>
+        <x:v>是否和普通 Outline 合并，还是保留采集专用版本</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="67.5" customHeight="1">
@@ -898,7 +901,7 @@
         <x:v>本地写作模板 + 质量循环</x:v>
       </x:c>
       <x:c r="E7" s="13" t="str">
-        <x:v>{{topic}}, {{target_reader}}, {{publish_goal}}, {{core_view}}, {{background}}, {{arguments}}, {{cases}}, {{scqa}}</x:v>
+        <x:v>{{topic}}, {{target_reader}}, {{publish_goal}}, {{core_view}}, {{outline}}, {{arguments}}, {{cases}}, {{scqa}}</x:v>
       </x:c>
       <x:c r="F7" s="13" t="str">
         <x:v>是否拆成“标题生成 / 正文生成 / 结尾生成”多个 Prompt</x:v>
